--- a/Deterministic/Model Files/Segment Test/data/production_capacity_scenarios_NEW_15YR_NO_MMR.xlsx
+++ b/Deterministic/Model Files/Segment Test/data/production_capacity_scenarios_NEW_15YR_NO_MMR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Deterministic/Model Files/Segment Test/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{F6FAFFEF-5053-401A-8268-13240819657F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5CD6D2C-C3A2-48C8-AE62-182D1B15889D}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="8_{F6FAFFEF-5053-401A-8268-13240819657F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11D8D8B2-B6BA-4354-821B-176CAB5ED7B3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Deterministic/Model Files/Segment Test/data/production_capacity_scenarios_NEW_15YR_NO_MMR.xlsx
+++ b/Deterministic/Model Files/Segment Test/data/production_capacity_scenarios_NEW_15YR_NO_MMR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Deterministic/Model Files/Segment Test/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="8_{F6FAFFEF-5053-401A-8268-13240819657F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11D8D8B2-B6BA-4354-821B-176CAB5ED7B3}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="8_{F6FAFFEF-5053-401A-8268-13240819657F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEB07261-5C85-413E-B736-20B740DF79E1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
